--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB5AF6E-4AC9-5846-8478-E1E199B01377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D15A7D-46FC-C44C-A932-FB1CC9883162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="529">
   <si>
     <t>Handelsname</t>
   </si>
@@ -920,9 +920,6 @@
   </si>
   <si>
     <t>Gebrauchsinformation 09/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasenspray, Lösung </t>
   </si>
   <si>
     <t>1-2 Sprühstöße pro Nasenloch</t>
@@ -2144,52 +2141,52 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>241</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>1</v>
@@ -2198,7 +2195,7 @@
         <v>2</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T1" s="6" t="s">
         <v>176</v>
@@ -2209,16 +2206,16 @@
     </row>
     <row r="2" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>148</v>
@@ -2239,16 +2236,16 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="6" t="s">
@@ -2270,22 +2267,22 @@
     </row>
     <row r="3" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>148</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
@@ -2300,7 +2297,7 @@
         <v>6</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>10</v>
@@ -2309,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O3" s="5"/>
       <c r="P3" s="6" t="s">
@@ -2331,16 +2328,16 @@
     </row>
     <row r="4" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>148</v>
@@ -2361,16 +2358,16 @@
         <v>6</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>470</v>
-      </c>
       <c r="N4" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
@@ -2392,16 +2389,16 @@
     </row>
     <row r="5" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>148</v>
@@ -2420,16 +2417,16 @@
         <v>6</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6" t="s">
@@ -2451,16 +2448,16 @@
     </row>
     <row r="6" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>148</v>
@@ -2479,16 +2476,16 @@
         <v>6</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6" t="s">
@@ -2510,16 +2507,16 @@
     </row>
     <row r="7" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>148</v>
@@ -2538,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>22</v>
@@ -2547,7 +2544,7 @@
         <v>256</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6" t="s">
@@ -2569,13 +2566,13 @@
     </row>
     <row r="8" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
@@ -2584,7 +2581,7 @@
         <v>148</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>25</v>
@@ -2606,7 +2603,7 @@
         <v>257</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6" t="s">
@@ -2628,13 +2625,13 @@
     </row>
     <row r="9" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>29</v>
@@ -2665,7 +2662,7 @@
         <v>32</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="6" t="s">
@@ -2687,13 +2684,13 @@
     </row>
     <row r="10" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
@@ -2720,13 +2717,13 @@
         <v>213</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6" t="s">
@@ -2748,13 +2745,13 @@
     </row>
     <row r="11" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>39</v>
@@ -2784,10 +2781,10 @@
         <v>27</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6" t="s">
@@ -2809,13 +2806,13 @@
     </row>
     <row r="12" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>41</v>
@@ -2824,7 +2821,7 @@
         <v>148</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>25</v>
@@ -2846,7 +2843,7 @@
         <v>32</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6" t="s">
@@ -2870,13 +2867,13 @@
     </row>
     <row r="13" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>43</v>
@@ -2898,7 +2895,7 @@
         <v>45</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>27</v>
@@ -2907,7 +2904,7 @@
         <v>46</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6" t="s">
@@ -2929,16 +2926,16 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>178</v>
@@ -2964,7 +2961,7 @@
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="6" t="s">
@@ -2986,13 +2983,13 @@
     </row>
     <row r="15" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>185</v>
@@ -3026,7 +3023,7 @@
         <v>33</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>34</v>
@@ -3049,16 +3046,16 @@
     </row>
     <row r="16" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>148</v>
@@ -3077,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>27</v>
@@ -3112,16 +3109,16 @@
     </row>
     <row r="17" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>148</v>
@@ -3134,16 +3131,16 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>57</v>
@@ -3171,13 +3168,13 @@
     </row>
     <row r="18" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>60</v>
@@ -3193,16 +3190,16 @@
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>260</v>
@@ -3230,16 +3227,16 @@
     </row>
     <row r="19" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>148</v>
@@ -3252,19 +3249,19 @@
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>189</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>191</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>58</v>
@@ -3289,16 +3286,16 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>148</v>
@@ -3313,13 +3310,13 @@
         <v>49</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>97</v>
@@ -3350,16 +3347,16 @@
     </row>
     <row r="21" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>148</v>
@@ -3374,13 +3371,13 @@
         <v>63</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>66</v>
@@ -3411,16 +3408,16 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>178</v>
@@ -3433,13 +3430,13 @@
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>71</v>
@@ -3468,16 +3465,16 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>178</v>
@@ -3490,13 +3487,13 @@
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>74</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>71</v>
@@ -3529,13 +3526,13 @@
     </row>
     <row r="24" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>76</v>
@@ -3553,13 +3550,13 @@
         <v>182</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>78</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>79</v>
@@ -3588,16 +3585,16 @@
     </row>
     <row r="25" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>178</v>
@@ -3612,13 +3609,13 @@
         <v>181</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>78</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>81</v>
@@ -3647,16 +3644,16 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>178</v>
@@ -3669,13 +3666,13 @@
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>82</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>83</v>
@@ -3706,13 +3703,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>85</v>
@@ -3728,13 +3725,13 @@
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>86</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>87</v>
@@ -3746,7 +3743,7 @@
         <v>75</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>12</v>
@@ -3767,13 +3764,13 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>89</v>
@@ -3789,7 +3786,7 @@
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>90</v>
@@ -3826,35 +3823,35 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>178</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>94</v>
@@ -3866,7 +3863,7 @@
         <v>75</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>12</v>
@@ -3887,13 +3884,13 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>96</v>
@@ -3909,13 +3906,13 @@
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>97</v>
@@ -3948,13 +3945,13 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>100</v>
@@ -3970,13 +3967,13 @@
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>102</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>97</v>
@@ -4007,13 +4004,13 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>399</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>400</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>104</v>
@@ -4029,13 +4026,13 @@
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>107</v>
@@ -4066,13 +4063,13 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>110</v>
@@ -4088,13 +4085,13 @@
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>112</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>113</v>
@@ -4125,13 +4122,13 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>193</v>
@@ -4140,20 +4137,20 @@
         <v>148</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>114</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>115</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>116</v>
@@ -4184,13 +4181,13 @@
     </row>
     <row r="35" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>194</v>
@@ -4206,13 +4203,13 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>118</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>97</v>
@@ -4245,13 +4242,13 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>195</v>
@@ -4267,13 +4264,13 @@
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>115</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>98</v>
@@ -4304,13 +4301,13 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>119</v>
@@ -4319,14 +4316,14 @@
         <v>148</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>120</v>
@@ -4363,13 +4360,13 @@
     </row>
     <row r="38" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>124</v>
@@ -4391,13 +4388,13 @@
         <v>127</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>200</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>287</v>
@@ -4424,13 +4421,13 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>288</v>
@@ -4452,19 +4449,19 @@
         <v>123</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>200</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>287</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>12</v>
@@ -4485,13 +4482,13 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>130</v>
@@ -4513,13 +4510,13 @@
         <v>123</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>200</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>287</v>
@@ -4544,13 +4541,13 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>131</v>
@@ -4572,19 +4569,19 @@
         <v>123</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>200</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>287</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>12</v>
@@ -4605,13 +4602,13 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>132</v>
@@ -4630,16 +4627,16 @@
         <v>123</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="L42" s="6" t="s">
+      <c r="M42" s="6" t="s">
         <v>520</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>521</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>287</v>
@@ -4664,13 +4661,13 @@
     </row>
     <row r="43" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>135</v>
@@ -4692,19 +4689,19 @@
         <v>123</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>200</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>291</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>34</v>
@@ -4727,13 +4724,13 @@
     </row>
     <row r="44" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>137</v>
@@ -4755,7 +4752,7 @@
         <v>123</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>210</v>
@@ -4786,16 +4783,16 @@
     </row>
     <row r="45" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>148</v>
@@ -4804,7 +4801,7 @@
         <v>140</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>294</v>
+        <v>126</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="s">
@@ -4814,7 +4811,7 @@
         <v>123</v>
       </c>
       <c r="K45" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>203</v>
@@ -4845,16 +4842,16 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>416</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>148</v>
@@ -4870,13 +4867,13 @@
         <v>123</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K46" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>142</v>
@@ -4893,7 +4890,7 @@
       </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T46" s="13">
         <v>45995</v>
@@ -4904,13 +4901,13 @@
     </row>
     <row r="47" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>143</v>
@@ -4919,7 +4916,7 @@
         <v>178</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>144</v>
@@ -4932,16 +4929,16 @@
         <v>145</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>146</v>
       </c>
       <c r="M47" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="N47" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6" t="s">
@@ -4954,7 +4951,7 @@
         <v>230</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="T47" s="13">
         <v>45995</v>
@@ -4963,22 +4960,22 @@
     </row>
     <row r="48" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>148</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>150</v>
@@ -4988,18 +4985,18 @@
         <v>123</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N48" s="6"/>
       <c r="O48" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>12</v>
@@ -5011,7 +5008,7 @@
         <v>237</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="T48" s="13">
         <v>45995</v>
@@ -5022,13 +5019,13 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>152</v>
@@ -5052,19 +5049,19 @@
         <v>155</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>156</v>
       </c>
       <c r="M49" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="N49" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="N49" s="6" t="s">
-        <v>305</v>
-      </c>
       <c r="O49" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>12</v>
@@ -5085,13 +5082,13 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>158</v>
@@ -5115,16 +5112,16 @@
         <v>159</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>160</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O50" s="6"/>
       <c r="P50" s="6" t="s">
@@ -5137,7 +5134,7 @@
         <v>231</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="T50" s="13">
         <v>45995</v>
@@ -5146,13 +5143,13 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>161</v>
@@ -5174,13 +5171,13 @@
         <v>163</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>164</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>33</v>
@@ -5205,13 +5202,13 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>165</v>
@@ -5227,13 +5224,13 @@
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>175</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>95</v>
@@ -5266,16 +5263,16 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>148</v>
@@ -5288,13 +5285,13 @@
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>175</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>95</v>
@@ -5318,7 +5315,7 @@
         <v>229</v>
       </c>
       <c r="S53" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T53" s="13">
         <v>45995</v>
@@ -5327,13 +5324,13 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>170</v>
@@ -5349,13 +5346,13 @@
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>172</v>
@@ -5379,7 +5376,7 @@
         <v>229</v>
       </c>
       <c r="S54" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T54" s="13">
         <v>45995</v>

--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D15A7D-46FC-C44C-A932-FB1CC9883162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3092EB64-D95A-594C-9006-385B4B5EAAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$U$54</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">

--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3092EB64-D95A-594C-9006-385B4B5EAAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2BA960-67A2-9840-B2E5-DBB3779FEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
+    <workbookView xWindow="-44160" yWindow="2820" windowWidth="36020" windowHeight="22600" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -246,9 +246,6 @@
     <t>6 bzw. 4 Lutschpastillen</t>
   </si>
   <si>
-    <t>Eukalyptusöl, Süßorangenöl, Myrtenöl, Zitronenöl</t>
-  </si>
-  <si>
     <t>magensaftresistente Weichkapsel</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
     <t>Eucabal® Balsam S als Creme</t>
   </si>
   <si>
-    <t>Eukalyptusöl, Kiefernnadelöl</t>
-  </si>
-  <si>
     <t>Erkältungskrankheiten der Atemwege</t>
   </si>
   <si>
@@ -393,9 +387,6 @@
     <t>1 Hartkapsel</t>
   </si>
   <si>
-    <t>Eibischwurzel Trockenextrakt, Bienenhonig</t>
-  </si>
-  <si>
     <t>trockener Husten, Reizhusten</t>
   </si>
   <si>
@@ -415,9 +406,6 @@
   </si>
   <si>
     <t>Nasic® Nasenspray</t>
-  </si>
-  <si>
-    <t>Xylometazolin, Dexpanthenol</t>
   </si>
   <si>
     <t>Nasenspray, Lösung</t>
@@ -502,9 +490,6 @@
     <t>Boxagrippal® Erkältungssaft</t>
   </si>
   <si>
-    <t>Ibuprofen, Pseudoephedrin</t>
-  </si>
-  <si>
     <t>Suspension zum Einnehmen</t>
   </si>
   <si>
@@ -529,9 +514,6 @@
     <t>Aspirin® Complex</t>
   </si>
   <si>
-    <t>Acetylsalicylsäure, Pseudoephedrin</t>
-  </si>
-  <si>
     <t>Rhinosinusitis mit Schmerzen und Fieber im Rahmen einer Erkältung bzw. eines grippalen Infekts</t>
   </si>
   <si>
@@ -541,24 +523,15 @@
     <t>Wick MediNait</t>
   </si>
   <si>
-    <t>Paracetamol, Dextromethorphan, Ephedrin, Doxylamin</t>
-  </si>
-  <si>
     <t>30 ml</t>
   </si>
   <si>
     <t>enthält Ethanol, kann Reaktionsfähigkeit beeinträchtigen</t>
   </si>
   <si>
-    <t>Paracetamol, Dextromethorphan, Doxylamin</t>
-  </si>
-  <si>
     <t>Grippostad® C</t>
   </si>
   <si>
-    <t>Paracetamol, Ascorbinsäure, Coffein, Chlorphenamin</t>
-  </si>
-  <si>
     <t>2 Kapseln</t>
   </si>
   <si>
@@ -667,12 +640,6 @@
     <t>Pentoxyverin</t>
   </si>
   <si>
-    <t>Xylometazolin, Levomenthol, Cineol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meerwasser (isoton),  Dexpanthenol </t>
-  </si>
-  <si>
     <t>2 Sprühstöße pro Nasenloch</t>
   </si>
   <si>
@@ -802,12 +769,6 @@
     <t>Gebrauchsinformation 12/2020</t>
   </si>
   <si>
-    <t>Isländisches Moos Extrakt, Carbomer, Hyaluronsäure, Xanthan Gummi</t>
-  </si>
-  <si>
-    <t>Carbomer, Hyaluronsäure, Xanthan</t>
-  </si>
-  <si>
     <t>Halsschmerzen/Heiserkeit</t>
   </si>
   <si>
@@ -844,18 +805,12 @@
     <t>Fachinformation 01/2025</t>
   </si>
   <si>
-    <t>Thymian-Fluidextrakt, Efeublätter-Fluidextrakt</t>
-  </si>
-  <si>
     <t>Thymiankraut-Dickextrakt</t>
   </si>
   <si>
     <t>Fachinformation 09/2014</t>
   </si>
   <si>
-    <t>Primelwurzel-Trockenextrakt, Thymiankraut-Trockenextrakt</t>
-  </si>
-  <si>
     <t>Fachinformation 01/2024</t>
   </si>
   <si>
@@ -973,9 +928,6 @@
     <t>Fachinformation 12/2024</t>
   </si>
   <si>
-    <t>BNO 1016 (Enzianwurzel-Trockenextrakt, Primelblüten-Trockenextrakt, Sauerampferkraut-Trockenextrakt, Holunderblüten-Trockenextrakt, Eisenkraut-Trockenextrakt)</t>
-  </si>
-  <si>
     <t>Salz</t>
   </si>
   <si>
@@ -1408,9 +1360,6 @@
     <t>Einnahme unzerkaut mit reichlich Flüssigkeit, maximal 3-mal täglich, nicht auf nüchternen Magen, 4h Abstand zwischen den Einzeldosen</t>
   </si>
   <si>
-    <t>Acetylsalicylsäure, Ascorbinsäure</t>
-  </si>
-  <si>
     <t>maximal 4 Tage</t>
   </si>
   <si>
@@ -1429,15 +1378,6 @@
     <t>maximal 10 Tage</t>
   </si>
   <si>
-    <t>Tyrothricin, Cetrimoniumbromid, Lidocain</t>
-  </si>
-  <si>
-    <t>2,4-Dichlorbenzylalkohol, Amylmetacresol, Levomenthol</t>
-  </si>
-  <si>
-    <t>Thymian-Fluidextrakt, Primelwurzel-Fluidextrakt</t>
-  </si>
-  <si>
     <t>Einnahme aufgelöst in Wasser, maximal 3-mal täglich, nicht auf nüchternen Magen, 4h Abstand zwischen den Einzeldosen</t>
   </si>
   <si>
@@ -1628,6 +1568,66 @@
   </si>
   <si>
     <t>Einnahme mittels beigefügtem Messbecher, 1-mal täglich abends vor dem Schlafengehen</t>
+  </si>
+  <si>
+    <t>Acetylsalicylsäure; Ascorbinsäure</t>
+  </si>
+  <si>
+    <t>Tyrothricin; Cetrimoniumbromid; Lidocain</t>
+  </si>
+  <si>
+    <t>Isländisches Moos Extrakt; Carbomer; Hyaluronsäure; Xanthan Gummi</t>
+  </si>
+  <si>
+    <t>Carbomer; Hyaluronsäure; Xanthan</t>
+  </si>
+  <si>
+    <t>Eukalyptusöl; Süßorangenöl; Myrtenöl; Zitronenöl</t>
+  </si>
+  <si>
+    <t>Eukalyptusöl; Kiefernnadelöl</t>
+  </si>
+  <si>
+    <t>Thymian-Fluidextrakt; Efeublätter-Fluidextrakt</t>
+  </si>
+  <si>
+    <t>Primelwurzel-Trockenextrakt; Thymiankraut-Trockenextrakt</t>
+  </si>
+  <si>
+    <t>Thymian-Fluidextrakt; Primelwurzel-Fluidextrakt</t>
+  </si>
+  <si>
+    <t>Eibischwurzel Trockenextrakt; Bienenhonig</t>
+  </si>
+  <si>
+    <t>Xylometazolin; Dexpanthenol</t>
+  </si>
+  <si>
+    <t>Xylometazolin; Levomenthol; Cineol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meerwasser (isoton);  Dexpanthenol </t>
+  </si>
+  <si>
+    <t>BNO 1016 (Enzianwurzel-Trockenextrakt; Primelblüten-Trockenextrakt; Sauerampferkraut-Trockenextrakt; Holunderblüten-Trockenextrakt; Eisenkraut-Trockenextrakt)</t>
+  </si>
+  <si>
+    <t>Ibuprofen; Pseudoephedrin</t>
+  </si>
+  <si>
+    <t>Acetylsalicylsäure; Pseudoephedrin</t>
+  </si>
+  <si>
+    <t>Paracetamol; Dextromethorphan; Ephedrin; Doxylamin</t>
+  </si>
+  <si>
+    <t>Paracetamol; Dextromethorphan; Doxylamin</t>
+  </si>
+  <si>
+    <t>Paracetamol; Ascorbinsäure; Coffein; Chlorphenamin</t>
+  </si>
+  <si>
+    <t>2,4-Dichlorbenzylalkohol; Amylmetacresol; Levomenthol</t>
   </si>
 </sst>
 </file>
@@ -2144,52 +2144,52 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>1</v>
@@ -2198,30 +2198,30 @@
         <v>2</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>4</v>
@@ -2230,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -2239,16 +2239,16 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="6" t="s">
@@ -2258,10 +2258,10 @@
         <v>8</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="T2" s="13">
         <v>45995</v>
@@ -2270,28 +2270,28 @@
     </row>
     <row r="3" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -2300,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>10</v>
@@ -2309,7 +2309,7 @@
         <v>11</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="O3" s="5"/>
       <c r="P3" s="6" t="s">
@@ -2319,10 +2319,10 @@
         <v>13</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="T3" s="13">
         <v>45995</v>
@@ -2331,19 +2331,19 @@
     </row>
     <row r="4" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>4</v>
@@ -2352,7 +2352,7 @@
         <v>14</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -2361,16 +2361,16 @@
         <v>6</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
@@ -2380,10 +2380,10 @@
         <v>8</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="T4" s="13">
         <v>45995</v>
@@ -2392,19 +2392,19 @@
     </row>
     <row r="5" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>15</v>
@@ -2420,16 +2420,16 @@
         <v>6</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6" t="s">
@@ -2439,10 +2439,10 @@
         <v>18</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="T5" s="13">
         <v>45995</v>
@@ -2451,19 +2451,19 @@
     </row>
     <row r="6" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>19</v>
@@ -2479,16 +2479,16 @@
         <v>6</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6" t="s">
@@ -2498,10 +2498,10 @@
         <v>18</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="T6" s="13">
         <v>45995</v>
@@ -2510,19 +2510,19 @@
     </row>
     <row r="7" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>21</v>
@@ -2538,16 +2538,16 @@
         <v>6</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6" t="s">
@@ -2557,10 +2557,10 @@
         <v>23</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="T7" s="13">
         <v>45995</v>
@@ -2569,44 +2569,44 @@
     </row>
     <row r="8" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>462</v>
+        <v>510</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6" t="s">
@@ -2616,10 +2616,10 @@
         <v>28</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="T8" s="13">
         <v>45995</v>
@@ -2628,19 +2628,19 @@
     </row>
     <row r="9" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>30</v>
@@ -2650,13 +2650,13 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>27</v>
@@ -2665,7 +2665,7 @@
         <v>32</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="6" t="s">
@@ -2675,10 +2675,10 @@
         <v>8</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="T9" s="13">
         <v>45995</v>
@@ -2687,46 +2687,46 @@
     </row>
     <row r="10" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6" t="s">
@@ -2736,10 +2736,10 @@
         <v>38</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="T10" s="13">
         <v>45995</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="11" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>36</v>
@@ -2769,25 +2769,25 @@
         <v>25</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6" t="s">
@@ -2797,10 +2797,10 @@
         <v>38</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="T11" s="13">
         <v>45995</v>
@@ -2809,35 +2809,35 @@
     </row>
     <row r="12" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>463</v>
+        <v>528</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>27</v>
@@ -2846,43 +2846,43 @@
         <v>32</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="T12" s="13">
         <v>45995</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>44</v>
@@ -2892,13 +2892,13 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>27</v>
@@ -2907,7 +2907,7 @@
         <v>46</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6" t="s">
@@ -2917,10 +2917,10 @@
         <v>47</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="T13" s="13">
         <v>45995</v>
@@ -2929,19 +2929,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>48</v>
@@ -2951,20 +2951,20 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>50</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>51</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="6" t="s">
@@ -2974,10 +2974,10 @@
         <v>52</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="T14" s="13">
         <v>45995</v>
@@ -2986,35 +2986,35 @@
     </row>
     <row r="15" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>253</v>
+        <v>511</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>66</v>
@@ -3026,7 +3026,7 @@
         <v>33</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>34</v>
@@ -3035,49 +3035,49 @@
         <v>8</v>
       </c>
       <c r="R15" s="19" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="T15" s="13">
         <v>45995</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>254</v>
+        <v>512</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>53</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>27</v>
@@ -3098,33 +3098,33 @@
         <v>8</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="T16" s="13">
         <v>45995</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>55</v>
@@ -3134,16 +3134,16 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>57</v>
@@ -3159,10 +3159,10 @@
         <v>59</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="T17" s="13">
         <v>45995</v>
@@ -3171,19 +3171,19 @@
     </row>
     <row r="18" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>60</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>55</v>
@@ -3193,19 +3193,19 @@
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>58</v>
@@ -3218,10 +3218,10 @@
         <v>59</v>
       </c>
       <c r="R18" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="S18" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="T18" s="13">
         <v>45995</v>
@@ -3230,19 +3230,19 @@
     </row>
     <row r="19" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>61</v>
@@ -3252,19 +3252,19 @@
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>58</v>
@@ -3277,10 +3277,10 @@
         <v>47</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="T19" s="13">
         <v>45995</v>
@@ -3289,19 +3289,19 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>30</v>
@@ -3313,16 +3313,16 @@
         <v>49</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>65</v>
@@ -3338,10 +3338,10 @@
         <v>47</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="T20" s="13">
         <v>45995</v>
@@ -3350,19 +3350,19 @@
     </row>
     <row r="21" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>30</v>
@@ -3374,13 +3374,13 @@
         <v>63</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>66</v>
@@ -3399,10 +3399,10 @@
         <v>47</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="T21" s="13">
         <v>45995</v>
@@ -3411,41 +3411,41 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F22" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="L22" s="6" t="s">
+      <c r="M22" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
@@ -3456,10 +3456,10 @@
         <v>47</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="T22" s="13">
         <v>45995</v>
@@ -3468,101 +3468,101 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="N23" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q23" s="16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="T23" s="13">
         <v>45995</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="K24" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="6" t="s">
@@ -3573,55 +3573,55 @@
         <v>12</v>
       </c>
       <c r="Q24" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="T24" s="13">
         <v>45995</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>77</v>
+        <v>514</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6" t="s">
@@ -3635,10 +3635,10 @@
         <v>38</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="T25" s="13">
         <v>45995</v>
@@ -3647,44 +3647,44 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="N26" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6" t="s">
@@ -3694,10 +3694,10 @@
         <v>47</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="T26" s="13">
         <v>45995</v>
@@ -3706,47 +3706,47 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>267</v>
+        <v>515</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>62</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M27" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K27" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="N27" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>12</v>
@@ -3755,10 +3755,10 @@
         <v>47</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="T27" s="13">
         <v>45995</v>
@@ -3767,44 +3767,44 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>270</v>
+        <v>516</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6" t="s">
@@ -3814,10 +3814,10 @@
         <v>47</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="T28" s="13">
         <v>45995</v>
@@ -3826,47 +3826,47 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>12</v>
@@ -3875,10 +3875,10 @@
         <v>47</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="T29" s="13">
         <v>45995</v>
@@ -3887,47 +3887,47 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="L30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>12</v>
@@ -3936,10 +3936,10 @@
         <v>47</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="T30" s="13">
         <v>45995</v>
@@ -3948,44 +3948,44 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6" t="s">
@@ -3995,10 +3995,10 @@
         <v>47</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S31" s="6" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="T31" s="13">
         <v>45995</v>
@@ -4007,45 +4007,45 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>12</v>
@@ -4054,10 +4054,10 @@
         <v>38</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="T32" s="13">
         <v>45995</v>
@@ -4066,44 +4066,44 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6" t="s">
@@ -4113,10 +4113,10 @@
         <v>52</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="T33" s="13">
         <v>45995</v>
@@ -4125,44 +4125,44 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6" t="s">
@@ -4172,10 +4172,10 @@
         <v>47</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="T34" s="13">
         <v>45995</v>
@@ -4184,44 +4184,44 @@
     </row>
     <row r="35" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>117</v>
+        <v>518</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6" t="s">
@@ -4231,58 +4231,58 @@
         <v>52</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="T35" s="13">
         <v>45995</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6" t="s">
@@ -4292,10 +4292,10 @@
         <v>47</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="T36" s="13">
         <v>45995</v>
@@ -4304,44 +4304,44 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O37" s="6"/>
       <c r="P37" s="6" t="s">
@@ -4351,10 +4351,10 @@
         <v>47</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="T37" s="13">
         <v>45995</v>
@@ -4363,108 +4363,108 @@
     </row>
     <row r="38" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>125</v>
+        <v>519</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J38" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="K38" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6" t="s">
         <v>34</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="T38" s="13">
         <v>45995</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>12</v>
@@ -4473,10 +4473,10 @@
         <v>8</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="T39" s="13">
         <v>45995</v>
@@ -4485,44 +4485,44 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="6" t="s">
@@ -4532,10 +4532,10 @@
         <v>8</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="T40" s="13">
         <v>45995</v>
@@ -4544,47 +4544,47 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>12</v>
@@ -4593,10 +4593,10 @@
         <v>8</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="T41" s="13">
         <v>45995</v>
@@ -4605,44 +4605,44 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>369</v>
-      </c>
       <c r="D42" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="6" t="s">
@@ -4652,10 +4652,10 @@
         <v>8</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="S42" s="6" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="T42" s="13">
         <v>45995</v>
@@ -4664,297 +4664,297 @@
     </row>
     <row r="43" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>34</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S43" s="6" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="T43" s="13">
         <v>45995</v>
       </c>
       <c r="U43" s="6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6" t="s">
         <v>34</v>
       </c>
       <c r="Q44" s="20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="T44" s="13">
         <v>45995</v>
       </c>
       <c r="U44" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K45" s="21" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q45" s="20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="R45" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="T45" s="13">
         <v>45995</v>
       </c>
       <c r="U45" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="K46" s="21" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="O46" s="6"/>
       <c r="P46" s="6" t="s">
         <v>34</v>
       </c>
       <c r="Q46" s="20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="T46" s="13">
         <v>45995</v>
       </c>
       <c r="U46" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>310</v>
+        <v>522</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="T47" s="13">
         <v>45995</v>
@@ -4963,120 +4963,120 @@
     </row>
     <row r="48" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="N48" s="6"/>
       <c r="O48" s="6" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q48" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="T48" s="13">
         <v>45995</v>
       </c>
       <c r="U48" s="6" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>153</v>
+        <v>523</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>16</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q49" s="18" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="T49" s="13">
         <v>45995</v>
@@ -5085,59 +5085,59 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>153</v>
+        <v>523</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H50" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="I50" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="K50" s="6" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="O50" s="6"/>
       <c r="P50" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q50" s="18" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="T50" s="13">
         <v>45995</v>
@@ -5146,41 +5146,41 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>162</v>
+        <v>524</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>33</v>
@@ -5190,13 +5190,13 @@
         <v>12</v>
       </c>
       <c r="Q51" s="18" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="S51" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="T51" s="13">
         <v>45995</v>
@@ -5205,59 +5205,59 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>166</v>
+        <v>525</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>33</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="T52" s="13">
         <v>45995</v>
@@ -5266,59 +5266,59 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>169</v>
+        <v>526</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>33</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="S53" s="6" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="T53" s="13">
         <v>45995</v>
@@ -5327,59 +5327,59 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>171</v>
+        <v>527</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="S54" s="6" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="T54" s="13">
         <v>45995</v>

--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2BA960-67A2-9840-B2E5-DBB3779FEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C23D285-5C12-A141-8502-3478B16831C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-44160" yWindow="2820" windowWidth="36020" windowHeight="22600" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
+    <workbookView xWindow="-51200" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -568,9 +568,6 @@
     <t xml:space="preserve">Fragen </t>
   </si>
   <si>
-    <t>Fieber/Schmerzen, Schnupfen</t>
-  </si>
-  <si>
     <t>Isla® med hydro+ Pastillen</t>
   </si>
   <si>
@@ -1423,18 +1420,6 @@
     <t>Husten</t>
   </si>
   <si>
-    <t>Husten, Halsschmerzen/Heiserkeit</t>
-  </si>
-  <si>
-    <t>Husten, Schnupfen</t>
-  </si>
-  <si>
-    <t>Fieber/Schmerzen, Halsschmerzen/Heiserkeit, Schnupfen, Husten</t>
-  </si>
-  <si>
-    <t>Fieber/Schmerzen, Schnupfen, Husten</t>
-  </si>
-  <si>
     <t>½-1 Brausetablette</t>
   </si>
   <si>
@@ -1628,6 +1613,21 @@
   </si>
   <si>
     <t>2,4-Dichlorbenzylalkohol; Amylmetacresol; Levomenthol</t>
+  </si>
+  <si>
+    <t>Husten; Halsschmerzen/Heiserkeit</t>
+  </si>
+  <si>
+    <t>Husten; Schnupfen</t>
+  </si>
+  <si>
+    <t>Fieber/Schmerzen; Schnupfen</t>
+  </si>
+  <si>
+    <t>Fieber/Schmerzen; Halsschmerzen/Heiserkeit; Schnupfen; Husten</t>
+  </si>
+  <si>
+    <t>Fieber/Schmerzen; Schnupfen; Husten</t>
   </si>
 </sst>
 </file>
@@ -2144,52 +2144,52 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>433</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>434</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>1</v>
@@ -2198,7 +2198,7 @@
         <v>2</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T1" s="6" t="s">
         <v>167</v>
@@ -2209,16 +2209,16 @@
     </row>
     <row r="2" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>144</v>
@@ -2239,16 +2239,16 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="6" t="s">
@@ -2258,10 +2258,10 @@
         <v>8</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T2" s="13">
         <v>45995</v>
@@ -2270,22 +2270,22 @@
     </row>
     <row r="3" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
@@ -2300,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>10</v>
@@ -2309,7 +2309,7 @@
         <v>11</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O3" s="5"/>
       <c r="P3" s="6" t="s">
@@ -2319,10 +2319,10 @@
         <v>13</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T3" s="13">
         <v>45995</v>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="4" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>144</v>
@@ -2361,16 +2361,16 @@
         <v>6</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="N4" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
@@ -2380,10 +2380,10 @@
         <v>8</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T4" s="13">
         <v>45995</v>
@@ -2392,16 +2392,16 @@
     </row>
     <row r="5" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>144</v>
@@ -2420,16 +2420,16 @@
         <v>6</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6" t="s">
@@ -2439,10 +2439,10 @@
         <v>18</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T5" s="13">
         <v>45995</v>
@@ -2451,16 +2451,16 @@
     </row>
     <row r="6" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>144</v>
@@ -2479,16 +2479,16 @@
         <v>6</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6" t="s">
@@ -2498,10 +2498,10 @@
         <v>18</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="T6" s="13">
         <v>45995</v>
@@ -2510,16 +2510,16 @@
     </row>
     <row r="7" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>144</v>
@@ -2538,16 +2538,16 @@
         <v>6</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6" t="s">
@@ -2557,10 +2557,10 @@
         <v>23</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T7" s="13">
         <v>45995</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="8" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
@@ -2584,29 +2584,29 @@
         <v>144</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6" t="s">
@@ -2616,10 +2616,10 @@
         <v>28</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T8" s="13">
         <v>45995</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="9" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>29</v>
@@ -2650,13 +2650,13 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>27</v>
@@ -2665,7 +2665,7 @@
         <v>32</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="6" t="s">
@@ -2675,10 +2675,10 @@
         <v>8</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T9" s="13">
         <v>45995</v>
@@ -2687,13 +2687,13 @@
     </row>
     <row r="10" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
@@ -2705,28 +2705,28 @@
         <v>36</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6" t="s">
@@ -2736,10 +2736,10 @@
         <v>38</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T10" s="13">
         <v>45995</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="11" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>39</v>
@@ -2769,25 +2769,25 @@
         <v>25</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6" t="s">
@@ -2797,10 +2797,10 @@
         <v>38</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T11" s="13">
         <v>45995</v>
@@ -2809,13 +2809,13 @@
     </row>
     <row r="12" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>41</v>
@@ -2824,20 +2824,20 @@
         <v>144</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>27</v>
@@ -2846,37 +2846,37 @@
         <v>32</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T12" s="13">
         <v>45995</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>43</v>
@@ -2892,13 +2892,13 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>27</v>
@@ -2907,7 +2907,7 @@
         <v>46</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6" t="s">
@@ -2917,10 +2917,10 @@
         <v>47</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T13" s="13">
         <v>45995</v>
@@ -2929,16 +2929,16 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>169</v>
@@ -2951,20 +2951,20 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>50</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>51</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="6" t="s">
@@ -2974,10 +2974,10 @@
         <v>52</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T14" s="13">
         <v>45995</v>
@@ -2986,35 +2986,35 @@
     </row>
     <row r="15" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>66</v>
@@ -3026,7 +3026,7 @@
         <v>33</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>34</v>
@@ -3035,49 +3035,49 @@
         <v>8</v>
       </c>
       <c r="R15" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T15" s="13">
         <v>45995</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>53</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>27</v>
@@ -3098,30 +3098,30 @@
         <v>8</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T16" s="13">
         <v>45995</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>144</v>
@@ -3134,16 +3134,16 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>57</v>
@@ -3159,10 +3159,10 @@
         <v>59</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T17" s="13">
         <v>45995</v>
@@ -3171,13 +3171,13 @@
     </row>
     <row r="18" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>60</v>
@@ -3193,19 +3193,19 @@
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>58</v>
@@ -3218,10 +3218,10 @@
         <v>59</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T18" s="13">
         <v>45995</v>
@@ -3230,16 +3230,16 @@
     </row>
     <row r="19" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>144</v>
@@ -3252,19 +3252,19 @@
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>58</v>
@@ -3277,10 +3277,10 @@
         <v>47</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T19" s="13">
         <v>45995</v>
@@ -3289,16 +3289,16 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>144</v>
@@ -3313,13 +3313,13 @@
         <v>49</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>95</v>
@@ -3338,10 +3338,10 @@
         <v>47</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="T20" s="13">
         <v>45995</v>
@@ -3350,16 +3350,16 @@
     </row>
     <row r="21" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>144</v>
@@ -3374,13 +3374,13 @@
         <v>63</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>460</v>
+        <v>524</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>64</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>66</v>
@@ -3399,10 +3399,10 @@
         <v>47</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="T21" s="13">
         <v>45995</v>
@@ -3411,35 +3411,35 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>68</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>69</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>70</v>
@@ -3456,10 +3456,10 @@
         <v>47</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T22" s="13">
         <v>45995</v>
@@ -3468,16 +3468,16 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>169</v>
@@ -3490,13 +3490,13 @@
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>73</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>70</v>
@@ -3512,30 +3512,30 @@
         <v>12</v>
       </c>
       <c r="Q23" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T23" s="13">
         <v>45995</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>75</v>
@@ -3544,7 +3544,7 @@
         <v>169</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>172</v>
@@ -3553,13 +3553,13 @@
         <v>173</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>76</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>77</v>
@@ -3577,33 +3577,33 @@
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T24" s="13">
         <v>45995</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>173</v>
@@ -3612,13 +3612,13 @@
         <v>172</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>76</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>79</v>
@@ -3635,10 +3635,10 @@
         <v>38</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T25" s="13">
         <v>45995</v>
@@ -3647,35 +3647,35 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>80</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>81</v>
@@ -3694,10 +3694,10 @@
         <v>47</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T26" s="13">
         <v>45995</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>83</v>
@@ -3721,20 +3721,20 @@
         <v>169</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>62</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>84</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>85</v>
@@ -3746,7 +3746,7 @@
         <v>74</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>12</v>
@@ -3755,10 +3755,10 @@
         <v>47</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T27" s="13">
         <v>45995</v>
@@ -3767,13 +3767,13 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>87</v>
@@ -3782,14 +3782,14 @@
         <v>169</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>88</v>
@@ -3814,10 +3814,10 @@
         <v>47</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T28" s="13">
         <v>45995</v>
@@ -3826,35 +3826,35 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>88</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>92</v>
@@ -3866,7 +3866,7 @@
         <v>74</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>12</v>
@@ -3875,10 +3875,10 @@
         <v>47</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T29" s="13">
         <v>45995</v>
@@ -3887,13 +3887,13 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>94</v>
@@ -3902,20 +3902,20 @@
         <v>169</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>95</v>
@@ -3936,10 +3936,10 @@
         <v>47</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T30" s="13">
         <v>45995</v>
@@ -3948,13 +3948,13 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>98</v>
@@ -3963,20 +3963,20 @@
         <v>169</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>100</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>95</v>
@@ -3995,10 +3995,10 @@
         <v>47</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S31" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T31" s="13">
         <v>45995</v>
@@ -4007,13 +4007,13 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>102</v>
@@ -4029,13 +4029,13 @@
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>105</v>
@@ -4054,10 +4054,10 @@
         <v>38</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T32" s="13">
         <v>45995</v>
@@ -4066,13 +4066,13 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>108</v>
@@ -4081,26 +4081,26 @@
         <v>169</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>109</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>110</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>111</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>74</v>
@@ -4113,10 +4113,10 @@
         <v>52</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T33" s="13">
         <v>45995</v>
@@ -4125,41 +4125,41 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>112</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>113</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>114</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>119</v>
@@ -4172,10 +4172,10 @@
         <v>47</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T34" s="13">
         <v>45995</v>
@@ -4184,35 +4184,35 @@
     </row>
     <row r="35" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>115</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>95</v>
@@ -4231,55 +4231,55 @@
         <v>52</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T35" s="13">
         <v>45995</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>113</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>96</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>91</v>
@@ -4292,10 +4292,10 @@
         <v>47</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T36" s="13">
         <v>45995</v>
@@ -4304,13 +4304,13 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>116</v>
@@ -4319,26 +4319,26 @@
         <v>144</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>117</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>118</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>119</v>
@@ -4351,10 +4351,10 @@
         <v>47</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T37" s="13">
         <v>45995</v>
@@ -4363,13 +4363,13 @@
     </row>
     <row r="38" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>121</v>
@@ -4378,7 +4378,7 @@
         <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>122</v>
@@ -4391,16 +4391,16 @@
         <v>123</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6" t="s">
@@ -4410,30 +4410,30 @@
         <v>124</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T38" s="13">
         <v>45995</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>144</v>
@@ -4452,19 +4452,19 @@
         <v>120</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>12</v>
@@ -4473,10 +4473,10 @@
         <v>8</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T39" s="13">
         <v>45995</v>
@@ -4485,13 +4485,13 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>126</v>
@@ -4513,16 +4513,16 @@
         <v>120</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="6" t="s">
@@ -4532,10 +4532,10 @@
         <v>8</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T40" s="13">
         <v>45995</v>
@@ -4544,13 +4544,13 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>127</v>
@@ -4572,19 +4572,19 @@
         <v>120</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>12</v>
@@ -4593,10 +4593,10 @@
         <v>8</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T41" s="13">
         <v>45995</v>
@@ -4605,13 +4605,13 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>128</v>
@@ -4630,19 +4630,19 @@
         <v>120</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="6" t="s">
@@ -4652,10 +4652,10 @@
         <v>8</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S42" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T42" s="13">
         <v>45995</v>
@@ -4664,13 +4664,13 @@
     </row>
     <row r="43" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>131</v>
@@ -4679,7 +4679,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>122</v>
@@ -4692,19 +4692,19 @@
         <v>120</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>34</v>
@@ -4713,27 +4713,27 @@
         <v>132</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S43" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T43" s="13">
         <v>45995</v>
       </c>
       <c r="U43" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>133</v>
@@ -4755,16 +4755,16 @@
         <v>120</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6" t="s">
@@ -4775,27 +4775,27 @@
       </c>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T44" s="13">
         <v>45995</v>
       </c>
       <c r="U44" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>144</v>
@@ -4814,10 +4814,10 @@
         <v>120</v>
       </c>
       <c r="K45" s="21" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6" t="s">
@@ -4831,36 +4831,36 @@
         <v>137</v>
       </c>
       <c r="R45" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T45" s="13">
         <v>45995</v>
       </c>
       <c r="U45" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>399</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>122</v>
@@ -4870,19 +4870,19 @@
         <v>120</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="K46" s="21" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>138</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O46" s="6"/>
       <c r="P46" s="6" t="s">
@@ -4893,24 +4893,24 @@
       </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T46" s="13">
         <v>45995</v>
       </c>
       <c r="U46" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>139</v>
@@ -4919,7 +4919,7 @@
         <v>169</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>140</v>
@@ -4932,16 +4932,16 @@
         <v>141</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>142</v>
       </c>
       <c r="M47" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="N47" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6" t="s">
@@ -4951,10 +4951,10 @@
         <v>145</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T47" s="13">
         <v>45995</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="48" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>146</v>
@@ -4988,18 +4988,18 @@
         <v>120</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N48" s="6"/>
       <c r="O48" s="6" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>12</v>
@@ -5008,27 +5008,27 @@
         <v>147</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T48" s="13">
         <v>45995</v>
       </c>
       <c r="U48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>148</v>
@@ -5037,7 +5037,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>149</v>
@@ -5046,25 +5046,25 @@
         <v>16</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>175</v>
+        <v>526</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>150</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>151</v>
       </c>
       <c r="M49" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="N49" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="N49" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="O49" s="6" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>12</v>
@@ -5073,10 +5073,10 @@
         <v>152</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T49" s="13">
         <v>45995</v>
@@ -5085,13 +5085,13 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>153</v>
@@ -5100,7 +5100,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>16</v>
@@ -5109,22 +5109,22 @@
         <v>149</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>175</v>
+        <v>526</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>154</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>155</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O50" s="6"/>
       <c r="P50" s="6" t="s">
@@ -5134,10 +5134,10 @@
         <v>152</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T50" s="13">
         <v>45995</v>
@@ -5146,13 +5146,13 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>156</v>
@@ -5161,26 +5161,26 @@
         <v>144</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>175</v>
+        <v>526</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>157</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>158</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>33</v>
@@ -5193,10 +5193,10 @@
         <v>152</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S51" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T51" s="13">
         <v>45995</v>
@@ -5205,13 +5205,13 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>159</v>
@@ -5220,20 +5220,20 @@
         <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="s">
-        <v>462</v>
+        <v>527</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>166</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>93</v>
@@ -5254,10 +5254,10 @@
         <v>145</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T52" s="13">
         <v>45995</v>
@@ -5266,35 +5266,35 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>144</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>462</v>
+        <v>527</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>166</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>93</v>
@@ -5315,10 +5315,10 @@
         <v>145</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S53" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T53" s="13">
         <v>45995</v>
@@ -5327,13 +5327,13 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>162</v>
@@ -5342,20 +5342,20 @@
         <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>112</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>463</v>
+        <v>528</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>163</v>
@@ -5376,10 +5376,10 @@
         <v>145</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S54" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T54" s="13">
         <v>45995</v>

--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C23D285-5C12-A141-8502-3478B16831C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CA2D77-317A-F74D-902E-614410230F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
@@ -1567,9 +1567,6 @@
     <t>Carbomer; Hyaluronsäure; Xanthan</t>
   </si>
   <si>
-    <t>Eukalyptusöl; Süßorangenöl; Myrtenöl; Zitronenöl</t>
-  </si>
-  <si>
     <t>Eukalyptusöl; Kiefernnadelöl</t>
   </si>
   <si>
@@ -1628,6 +1625,9 @@
   </si>
   <si>
     <t>Fieber/Schmerzen; Schnupfen; Husten</t>
+  </si>
+  <si>
+    <t>Eukalyptusöl; Süßorangenöl; Myrtenöl (Cineol); Zitronenöl</t>
   </si>
 </sst>
 </file>
@@ -2824,7 +2824,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>25</v>
@@ -3374,7 +3374,7 @@
         <v>63</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>64</v>
@@ -3426,14 +3426,14 @@
         <v>169</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>68</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>69</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>73</v>
@@ -3544,7 +3544,7 @@
         <v>169</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>172</v>
@@ -3553,7 +3553,7 @@
         <v>173</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>76</v>
@@ -3603,7 +3603,7 @@
         <v>169</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>173</v>
@@ -3612,7 +3612,7 @@
         <v>172</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>76</v>
@@ -3721,7 +3721,7 @@
         <v>169</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>62</v>
@@ -3782,7 +3782,7 @@
         <v>169</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>16</v>
@@ -3841,7 +3841,7 @@
         <v>169</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>63</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>472</v>
@@ -4199,7 +4199,7 @@
         <v>169</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>99</v>
@@ -4378,7 +4378,7 @@
         <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>122</v>
@@ -4679,7 +4679,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>122</v>
@@ -4860,7 +4860,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>122</v>
@@ -4919,7 +4919,7 @@
         <v>169</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>140</v>
@@ -5037,7 +5037,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>149</v>
@@ -5046,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>150</v>
@@ -5100,7 +5100,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>16</v>
@@ -5109,7 +5109,7 @@
         <v>149</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>154</v>
@@ -5161,14 +5161,14 @@
         <v>144</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>157</v>
@@ -5220,14 +5220,14 @@
         <v>144</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>166</v>
@@ -5281,14 +5281,14 @@
         <v>144</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>99</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>166</v>
@@ -5342,14 +5342,14 @@
         <v>144</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>112</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>473</v>

--- a/app/data/data_full.xlsx
+++ b/app/data/data_full.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CA2D77-317A-F74D-902E-614410230F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606C660A-E16C-3A47-81FB-EDCA9A8F6DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{E74A96DB-41C0-C44B-999C-C5BA6423010C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="529">
   <si>
     <t>Handelsname</t>
   </si>
@@ -2119,9 +2119,9 @@
   <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="37.83203125" style="4" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.83203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="51.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.1640625" customWidth="1"/>
     <col min="6" max="6" width="49.83203125" bestFit="1" customWidth="1"/>
@@ -2962,7 +2962,9 @@
       <c r="L14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M14" s="6"/>
+      <c r="M14" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="N14" s="6" t="s">
         <v>443</v>
       </c>
